--- a/Planejamento_Bebe_Heber.xlsx
+++ b/Planejamento_Bebe_Heber.xlsx
@@ -10,6 +10,7 @@
     <sheet name="01_Itens" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="02_Plano_Semanal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="03_Orcamento" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_Config" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,17 +19,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +48,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,83 +420,3753 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Qtd</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Unidade</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Marca/Modelo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Loja/Link</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Preço Unitário (R$)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Custo Estimado (R$)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Total (R$)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Data da Compra</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Garantia (meses)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Notas/Observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Saída de maternidade (kit)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J2" t="n">
+        <v>120</v>
+      </c>
+      <c r="K2" t="n">
+        <v>120</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Kit com manta, body e touquinha</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Body manga curta RN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>175</v>
+      </c>
+      <c r="K3" t="n">
+        <v>175</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Tamanho RN — comprar no 3° tri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Body manga longa RN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>40</v>
+      </c>
+      <c r="J4" t="n">
+        <v>160</v>
+      </c>
+      <c r="K4" t="n">
+        <v>160</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Para noites mais frias</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Macacão com pé (tamanho P)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>55</v>
+      </c>
+      <c r="J5" t="n">
+        <v>165</v>
+      </c>
+      <c r="K5" t="n">
+        <v>165</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Macacão sem pé (tamanho P)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J6" t="n">
+        <v>135</v>
+      </c>
+      <c r="K6" t="n">
+        <v>135</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Meias antiderrapantes bebê</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>par</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>90</v>
+      </c>
+      <c r="K7" t="n">
+        <v>90</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Touquinha de algodão</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>18</v>
+      </c>
+      <c r="J8" t="n">
+        <v>54</v>
+      </c>
+      <c r="K8" t="n">
+        <v>54</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Luvas anti-arranhão</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>par</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>36</v>
+      </c>
+      <c r="K9" t="n">
+        <v>36</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Evita arranhões no rosto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mijão (pijama com pé)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="J10" t="n">
+        <v>180</v>
+      </c>
+      <c r="K10" t="n">
+        <v>180</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Roupas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Casaco de plush</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>80</v>
+      </c>
+      <c r="J11" t="n">
+        <v>160</v>
+      </c>
+      <c r="K11" t="n">
+        <v>160</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Para dias frios</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fraldas descartáveis RN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J12" t="n">
+        <v>180</v>
+      </c>
+      <c r="K12" t="n">
+        <v>180</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Pacote c/ ~70 fraldas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fraldas descartáveis P</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J13" t="n">
+        <v>200</v>
+      </c>
+      <c r="K13" t="n">
+        <v>200</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Pacote c/ ~70 fraldas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lenços umedecidos s/ álcool</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>22</v>
+      </c>
+      <c r="J14" t="n">
+        <v>132</v>
+      </c>
+      <c r="K14" t="n">
+        <v>132</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sem perfume e álcool</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pomada para assaduras</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>30</v>
+      </c>
+      <c r="J15" t="n">
+        <v>90</v>
+      </c>
+      <c r="K15" t="n">
+        <v>90</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Bepantol Baby ou similar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Termômetro digital</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Axilar ou auricular</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Aspirador nasal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>45</v>
+      </c>
+      <c r="J17" t="n">
+        <v>45</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Manual tipo NoseFrida ou elétrico</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sabonete líquido bebê</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>25</v>
+      </c>
+      <c r="J18" t="n">
+        <v>50</v>
+      </c>
+      <c r="K18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Hipoalergênico</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Shampoo bebê</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>50</v>
+      </c>
+      <c r="K19" t="n">
+        <v>50</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sem lágrimas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Óleo de amêndoas / hidratante</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Algodão hidrófilo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24</v>
+      </c>
+      <c r="K21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tesoura/cortador de unhas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" t="n">
+        <v>30</v>
+      </c>
+      <c r="K22" t="n">
+        <v>30</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Específico para bebê</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cotonetes para bebê</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>caixa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" t="n">
+        <v>15</v>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Com proteção na ponta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Almofada de amamentação</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>120</v>
+      </c>
+      <c r="J24" t="n">
+        <v>120</v>
+      </c>
+      <c r="K24" t="n">
+        <v>120</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Formato C ou U</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sutiã para amamentação</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>80</v>
+      </c>
+      <c r="J25" t="n">
+        <v>240</v>
+      </c>
+      <c r="K25" t="n">
+        <v>240</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Comprar perto do parto — tamanho muda</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Protetor de seios (disco)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>caixa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>40</v>
+      </c>
+      <c r="J26" t="n">
+        <v>40</v>
+      </c>
+      <c r="K26" t="n">
+        <v>40</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Descartável ou lavável</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bomba tira-leite elétrica</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>450</v>
+      </c>
+      <c r="J27" t="n">
+        <v>450</v>
+      </c>
+      <c r="K27" t="n">
+        <v>450</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Medela Harmony / Philips Avent</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mamadeira 150 ml anti-cólica</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J28" t="n">
+        <v>130</v>
+      </c>
+      <c r="K28" t="n">
+        <v>130</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NUK ou MAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mamadeira 240 ml anti-cólica</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>70</v>
+      </c>
+      <c r="J29" t="n">
+        <v>140</v>
+      </c>
+      <c r="K29" t="n">
+        <v>140</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NUK ou MAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Esterilizador elétrico</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>250</v>
+      </c>
+      <c r="J30" t="n">
+        <v>250</v>
+      </c>
+      <c r="K30" t="n">
+        <v>250</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Capacidade 6 mamadeiras</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Babador impermeável</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" t="n">
+        <v>100</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Copo de treinamento</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>40</v>
+      </c>
+      <c r="J32" t="n">
+        <v>40</v>
+      </c>
+      <c r="K32" t="n">
+        <v>40</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Para introdução alimentar ~6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Colheres de silicone</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>18</v>
+      </c>
+      <c r="J33" t="n">
+        <v>36</v>
+      </c>
+      <c r="K33" t="n">
+        <v>36</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Para papinhas — a partir dos 6 meses</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Berço grade fixa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>700</v>
+      </c>
+      <c r="J34" t="n">
+        <v>700</v>
+      </c>
+      <c r="K34" t="n">
+        <v>700</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Com certificação INMETRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Colchão para berço</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>250</v>
+      </c>
+      <c r="J35" t="n">
+        <v>250</v>
+      </c>
+      <c r="K35" t="n">
+        <v>250</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Espuma D18 ou superior</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Trocador de fraldas</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>200</v>
+      </c>
+      <c r="J36" t="n">
+        <v>200</v>
+      </c>
+      <c r="K36" t="n">
+        <v>200</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Com bordas de segurança</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cômoda para quarto bebê</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>900</v>
+      </c>
+      <c r="J37" t="n">
+        <v>900</v>
+      </c>
+      <c r="K37" t="n">
+        <v>900</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Com ou sem trocador acoplado</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kit berço (6 peças)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>280</v>
+      </c>
+      <c r="J38" t="n">
+        <v>280</v>
+      </c>
+      <c r="K38" t="n">
+        <v>280</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Fronha, protetor, saia, lençol — sem itens soltos no berço</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Luminária noturna</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>80</v>
+      </c>
+      <c r="J39" t="n">
+        <v>80</v>
+      </c>
+      <c r="K39" t="n">
+        <v>80</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Luz âmbar — não perturba sono</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Monitor de bebê com câmera</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Manta para berço</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>60</v>
+      </c>
+      <c r="J41" t="n">
+        <v>120</v>
+      </c>
+      <c r="K41" t="n">
+        <v>120</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Fina, algodão — não colocar no berço RN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mobile musical</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>120</v>
+      </c>
+      <c r="J42" t="n">
+        <v>120</v>
+      </c>
+      <c r="K42" t="n">
+        <v>120</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Estimulação visual e auditiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Umidificador de ar</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>150</v>
+      </c>
+      <c r="J43" t="n">
+        <v>150</v>
+      </c>
+      <c r="K43" t="n">
+        <v>150</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Qualidade do ar no quarto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bebê conforto (cadeirinha 0+)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>800</v>
+      </c>
+      <c r="J44" t="n">
+        <v>800</v>
+      </c>
+      <c r="K44" t="n">
+        <v>800</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Grupo 0+, até 13 kg — INMETRO obrigatório</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Carrinho de bebê</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Reclinável plano para RN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mochila canguru ergonômica</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>180</v>
+      </c>
+      <c r="J46" t="n">
+        <v>180</v>
+      </c>
+      <c r="K46" t="n">
+        <v>180</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Frente e costas, até 20 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Banho</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Banheira com suporte/redutor</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>180</v>
+      </c>
+      <c r="J47" t="n">
+        <v>180</v>
+      </c>
+      <c r="K47" t="n">
+        <v>180</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Com redutor para RN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Banho</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Termômetro de banho</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>35</v>
+      </c>
+      <c r="J48" t="n">
+        <v>35</v>
+      </c>
+      <c r="K48" t="n">
+        <v>35</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Manter água a ~37 °C</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Banho</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Toalha com capuz</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>70</v>
+      </c>
+      <c r="J49" t="n">
+        <v>210</v>
+      </c>
+      <c r="K49" t="n">
+        <v>210</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>100% algodão</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Banho</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Esponja de banho bebê</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>20</v>
+      </c>
+      <c r="J50" t="n">
+        <v>40</v>
+      </c>
+      <c r="K50" t="n">
+        <v>40</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Macia</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Banho</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tina estilo balde (Puj/Stokke)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>220</v>
+      </c>
+      <c r="J51" t="n">
+        <v>220</v>
+      </c>
+      <c r="K51" t="n">
+        <v>220</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Opcional — banho de balde</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Saúde e Segurança</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Protetor de tomadas</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>60</v>
+      </c>
+      <c r="K52" t="n">
+        <v>60</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Instalar antes de engatinhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Saúde e Segurança</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tapete antiderrapante banheiro</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>45</v>
+      </c>
+      <c r="J53" t="n">
+        <v>45</v>
+      </c>
+      <c r="K53" t="n">
+        <v>45</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Saúde e Segurança</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Termômetro de ambiente</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>50</v>
+      </c>
+      <c r="J54" t="n">
+        <v>50</v>
+      </c>
+      <c r="K54" t="n">
+        <v>50</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Manter quarto a 20-22 °C</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Saúde e Segurança</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Kit primeiros socorros</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>80</v>
+      </c>
+      <c r="J55" t="n">
+        <v>80</v>
+      </c>
+      <c r="K55" t="n">
+        <v>80</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Gazes, soro fisiológico, esparadrapo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Saúde e Segurança</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cinto de segurança trocador</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>25</v>
+      </c>
+      <c r="J56" t="n">
+        <v>25</v>
+      </c>
+      <c r="K56" t="n">
+        <v>25</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Nunca deixar bebê sem cinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bolsa maternidade</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>200</v>
+      </c>
+      <c r="J57" t="n">
+        <v>200</v>
+      </c>
+      <c r="K57" t="n">
+        <v>200</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Grande, com muitos compartimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Absorvente pós-parto noturno</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>50</v>
+      </c>
+      <c r="K58" t="n">
+        <v>50</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Extra-absorção</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Calcinha descartável pós-parto</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>30</v>
+      </c>
+      <c r="J59" t="n">
+        <v>60</v>
+      </c>
+      <c r="K59" t="n">
+        <v>60</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Kit 5 un.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Cinta pós-parto</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>90</v>
+      </c>
+      <c r="J60" t="n">
+        <v>90</v>
+      </c>
+      <c r="K60" t="n">
+        <v>90</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Usar após orientação médica</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sutiã amamentação para dormir</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>60</v>
+      </c>
+      <c r="J61" t="n">
+        <v>120</v>
+      </c>
+      <c r="K61" t="n">
+        <v>120</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Confortável, sem arame</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Travesseiro de amamentação</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>120</v>
+      </c>
+      <c r="J62" t="n">
+        <v>120</v>
+      </c>
+      <c r="K62" t="n">
+        <v>120</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Pode ser a almofada de amamentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Creme preventivo de estrias</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>50</v>
+      </c>
+      <c r="J63" t="n">
+        <v>100</v>
+      </c>
+      <c r="K63" t="n">
+        <v>100</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Usar já agora durante a gestação</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Documentos e Serviços</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Plano de saúde infantil (cotação)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>400</v>
+      </c>
+      <c r="J64" t="n">
+        <v>400</v>
+      </c>
+      <c r="K64" t="n">
+        <v>400</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Incluir bebê em até 30 dias após o nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Documentos e Serviços</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Certidão de nascimento</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Registrar em cartório em até 15 dias — gratuito</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Documentos e Serviços</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Caderneta de vacinação</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Gratuita no SUS — disponível na maternidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chupeta ortodôntica 0-6 m</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>30</v>
+      </c>
+      <c r="J67" t="n">
+        <v>90</v>
+      </c>
+      <c r="K67" t="n">
+        <v>90</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>INMETRO, ortodôntica</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chocalho colorido</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>30</v>
+      </c>
+      <c r="J68" t="n">
+        <v>60</v>
+      </c>
+      <c r="K68" t="n">
+        <v>60</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Estimulação visual e auditiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tapete de atividades</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>150</v>
+      </c>
+      <c r="J69" t="n">
+        <v>150</v>
+      </c>
+      <c r="K69" t="n">
+        <v>150</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Com arcos e penduricalhos</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Livros de pano</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>35</v>
+      </c>
+      <c r="J70" t="n">
+        <v>105</v>
+      </c>
+      <c r="K70" t="n">
+        <v>105</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Estimulação sensorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mordedor de silicone</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>25</v>
+      </c>
+      <c r="J71" t="n">
+        <v>50</v>
+      </c>
+      <c r="K71" t="n">
+        <v>50</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>A comprar</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Para fase de dentição</t>
         </is>
       </c>
     </row>
@@ -518,35 +4181,357 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Semana #</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Itens sugeridos para cotar/comprar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Status da semana</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Roupas – Saída de maternidade (kit) (Alta)
+Higiene e Cuidados – Fraldas descartáveis RN (Alta)
+Higiene e Cuidados – Fraldas descartáveis P (Alta)
+Higiene e Cuidados – Lenços umedecidos s/ álcool (Alta)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados – Pomada para assaduras (Alta)
+Higiene e Cuidados – Termômetro digital (Alta)
+Higiene e Cuidados – Aspirador nasal (Alta)
+Alimentação – Almofada de amamentação (Alta)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Alimentação – Sutiã para amamentação (Alta)
+Alimentação – Protetor de seios (disco) (Alta)
+Móveis e Quarto – Berço grade fixa (Alta)
+Móveis e Quarto – Colchão para berço (Alta)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto – Trocador de fraldas (Alta)
+Móveis e Quarto – Cômoda para quarto bebê (Alta)
+Móveis e Quarto – Kit berço (6 peças) (Alta)
+Transporte – Bebê conforto (cadeirinha 0+) (Alta)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Transporte – Carrinho de bebê (Alta)
+Banho – Banheira com suporte/redutor (Alta)
+Banho – Termômetro de banho (Alta)
+Saúde e Segurança – Protetor de tomadas (Alta)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Saúde e Segurança – Tapete antiderrapante banheiro (Alta)
+Saúde e Segurança – Termômetro de ambiente (Alta)
+Saúde e Segurança – Kit primeiros socorros (Alta)
+Saúde e Segurança – Cinto de segurança trocador (Alta)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Maternidade e Mãe – Bolsa maternidade (Alta)
+Maternidade e Mãe – Absorvente pós-parto noturno (Alta)
+Maternidade e Mãe – Calcinha descartável pós-parto (Alta)
+Documentos e Serviços – Plano de saúde infantil (cotação) (Alta)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Documentos e Serviços – Certidão de nascimento (Alta)
+Documentos e Serviços – Caderneta de vacinação (Alta)
+Higiene e Cuidados – Sabonete líquido bebê (Média)
+Higiene e Cuidados – Shampoo bebê (Média)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Higiene e Cuidados – Óleo de amêndoas / hidratante (Média)
+Higiene e Cuidados – Algodão hidrófilo (Média)
+Higiene e Cuidados – Tesoura/cortador de unhas (Média)
+Alimentação – Bomba tira-leite elétrica (Média)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Alimentação – Mamadeira 150 ml anti-cólica (Média)
+Alimentação – Mamadeira 240 ml anti-cólica (Média)
+Alimentação – Esterilizador elétrico (Média)
+Móveis e Quarto – Luminária noturna (Média)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Móveis e Quarto – Monitor de bebê com câmera (Média)
+Móveis e Quarto – Manta para berço (Média)
+Transporte – Mochila canguru ergonômica (Média)
+Banho – Toalha com capuz (Média)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Banho – Esponja de banho bebê (Média)
+Maternidade e Mãe – Cinta pós-parto (Média)
+Maternidade e Mãe – Sutiã amamentação para dormir (Média)
+Maternidade e Mãe – Travesseiro de amamentação (Média)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos – Chupeta ortodôntica 0-6 m (Média)
+Roupas – Body manga curta RN (Baixa)
+Roupas – Body manga longa RN (Baixa)
+Roupas – Macacão com pé (tamanho P) (Baixa)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Roupas – Macacão sem pé (tamanho P) (Baixa)
+Roupas – Meias antiderrapantes bebê (Baixa)
+Roupas – Touquinha de algodão (Baixa)
+Roupas – Luvas anti-arranhão (Baixa)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Roupas – Mijão (pijama com pé) (Baixa)
+Roupas – Casaco de plush (Baixa)
+Higiene e Cuidados – Cotonetes para bebê (Baixa)
+Alimentação – Babador impermeável (Baixa)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Alimentação – Copo de treinamento (Baixa)
+Alimentação – Colheres de silicone (Baixa)
+Móveis e Quarto – Mobile musical (Baixa)
+Móveis e Quarto – Umidificador de ar (Baixa)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Banho – Tina estilo balde (Puj/Stokke) (Baixa)
+Maternidade e Mãe – Creme preventivo de estrias (Baixa)
+Brinquedos e Estímulos – Chocalho colorido (Baixa)
+Brinquedos e Estímulos – Tapete de atividades (Baixa)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brinquedos e Estímulos – Livros de pano (Baixa)
+Brinquedos e Estímulos – Mordedor de silicone (Baixa)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -559,33 +4544,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Mês</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Orçado (R$)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Previsto (R$)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Realizado (R$)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Diferença (R$)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Chave</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dpp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>semana_base</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>data_base</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
